--- a/SETxHES/docs/SETX_HES_ScenarioMatrix.xlsx
+++ b/SETxHES/docs/SETX_HES_ScenarioMatrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/peacock/Documents/HES -- Southeast Texas Hurricane Evacuation Study/1 Transportation analysis report/Darrell's Scenario Matrix/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C04DD5-7BF0-4249-9676-5A31E7CA55EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{717DCFFC-DB17-3948-93CB-4C76F1B0B50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{D0423A93-84CE-4BC8-8209-C13813B0CB9C}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="16860" xr2:uid="{D0423A93-84CE-4BC8-8209-C13813B0CB9C}"/>
   </bookViews>
   <sheets>
     <sheet name="ALLRegions-FULL" sheetId="5" r:id="rId1"/>
@@ -2318,7 +2318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2487,12 +2487,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2509,6 +2503,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2828,15 +2831,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>91755</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3217,27 +3220,27 @@
     <col min="21" max="21" width="17.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:28" ht="13" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="38"/>
     </row>
-    <row r="2" spans="1:28" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="76" t="s">
         <v>614</v>
       </c>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="71"/>
-      <c r="L2" s="71"/>
-      <c r="M2" s="71"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="78"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -7798,7 +7801,7 @@
   <dimension ref="A1:AB98"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="0.796875" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
@@ -7819,26 +7822,26 @@
     </row>
     <row r="2" spans="1:28" ht="43" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="70" t="s">
         <v>613</v>
       </c>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73"/>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73"/>
-      <c r="T2" s="74"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="72"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -12834,7 +12837,7 @@
   <dimension ref="A1:AB187"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="0.796875" customWidth="1"/>
     <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
@@ -12855,26 +12858,26 @@
     </row>
     <row r="2" spans="1:28" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="73" t="s">
         <v>612</v>
       </c>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="76"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="76"/>
-      <c r="Q2" s="76"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="76"/>
-      <c r="T2" s="77"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="75"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
@@ -22086,7 +22089,7 @@
   <dimension ref="A1:AB151"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="0.796875" customWidth="1"/>
     <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.796875" bestFit="1" customWidth="1"/>
@@ -29694,7 +29697,7 @@
   <dimension ref="A1:AB136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="11.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.3984375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="0.796875" customWidth="1"/>
     <col min="3" max="3" width="9.796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.796875" bestFit="1" customWidth="1"/>
